--- a/Result/checksun_type/文化印刷業.xlsx
+++ b/Result/checksun_type/文化印刷業.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>22.71</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>21.86</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>21.08</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>21.86</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>21.08</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>12645.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>4866.8</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>4866.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>2602.3</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>935.52</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>935.52</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>1375.582259952273</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>12645</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>12645.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>21.99</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>21.66</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>20.97</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>21.66</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>20.97</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>7786.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>2360.2</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>2360.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>1344.9</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>694.98</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>694.98</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>687.6020166755757</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>7786</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>7786.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>21.46</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>21.48</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>20.87</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>21.48</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>20.87</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>3707.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>820.4</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>820.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>659.5</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>579.76</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>579.76</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>200.8230256847368</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>3707</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>3707.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>21.23</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>21.36</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>20.79</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>21.36</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>20.79</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>122.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>115.2</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>115.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>416.9</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>628.1</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>628.1</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-64.71206950520195</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>122</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>21.43</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>21.34</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>20.71</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>21.34</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>20.71</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>74.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>295.4</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>295.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>441.8</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>627.74</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>627.74</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-57.62963157992846</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>74</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>21.5</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>21.3</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>20.63</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>20.63</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>112.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>337.8</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>337.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>522.3</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>629.48</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>629.48</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-40.31080484454031</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>112</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>21.66</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>21.26</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>20.55</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>21.26</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>20.55</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>87.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>329.6</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>329.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>613.6</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>638.44</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>638.4400000000001</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-18.20138076382364</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>87</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>21.73</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>21.24</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>20.46</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>21.24</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>20.46</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>181.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>498.6</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>498.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>635.8</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>637.64</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>637.64</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>16.7121315216225</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>181</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>181.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>21.85</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>21.22</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>20.37</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>21.22</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>20.37</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>1023.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>718.6</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>718.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>619.1</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>644.72</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>644.72</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>55.92028723220176</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>1023</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>1023.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>21.81</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>21.22</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>20.27</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>21.22</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>20.27</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>286.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>588.2</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>588.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>529.4</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>630.6</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>630.6</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>19.7204994175936</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>286</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>286.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>21.87</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>21.17</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>20.19</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>21.17</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>20.19</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>71.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>706.8</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>706.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>568.7</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>632.6</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>632.6</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>46.26649898895357</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>71</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>10.2</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>10.48</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>11.66</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>10.48</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>11.66</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>222569.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>161549.2</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>161549.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>190628.3</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>296261.56</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>296261.56</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-73741.36149537301</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>222569</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>222569.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>10.13</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>10.53</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>11.71</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>11.71</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>104042.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>129679.4</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>129679.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>181152.0</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>294956.46</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>294956.46</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-84265.52768455725</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>104042</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>104042.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>10.056</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>10.58</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>11.76</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>11.76</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>112936.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>155185.8</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>155185.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>213530.1</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>297255.84</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>297255.84</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-83591.24625180056</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>112936</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>112936.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>10.066</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>10.65</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>11.82</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>10.65</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>11.82</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>92752.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>153273.0</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>153273</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>305645.0</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>297549.6</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>297549.6</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-80595.51398172672</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>92752</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>92752.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>10.126</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>10.72</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>11.89</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>11.89</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>275447.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>213728.4</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>213728.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>367431.9</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>298570.28</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>298570.28</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-71274.91381084535</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>275447</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>275447.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>10.166</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>10.78</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>11.94</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>11.94</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>63220.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>219707.4</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>219707.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>437580.3</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>293585.6</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>293585.6</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-74988.70235919888</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>63220</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>63220.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>10.206</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>10.86</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>12</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>231574.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>232624.6</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>232624.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>560319.1</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>292334.6</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>292334.6</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-54877.3394868754</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>231574</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>231574.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>10.24</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>10.94</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>12.07</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>10.94</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>12.07</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>103372.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>271874.4</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>271874.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>866051.5</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>289084.0</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>289084</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-42224.84468759625</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>103372</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>103372.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>10.32</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>11.03</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>12.14</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>11.03</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>12.14</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>395029.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>458017.0</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>458017</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>862692.2</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>287573.14</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>287573.14</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-8905.893378354725</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>395029</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>395029.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>10.41</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>11.12</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>12.2</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>11.12</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>12.2</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>305342.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>521135.4</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>521135.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>840034.6</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>281583.6</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>281583.6</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>7761.711826931452</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>305342</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>305342.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>10.63</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>11.19</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>12.26</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>12.26</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>127806.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>655453.2</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>655453.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>861185.9</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>276774.32</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>276774.32</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>40904.69384066423</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>127806</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>127806.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>17.07</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>16.96</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>17.07</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>16.96</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>17.07</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>52.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>0</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>0</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-28.28442649673083</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>52</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>52.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>16.96</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>16.93</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>17.07</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>16.93</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>17.07</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>17.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>0</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>0</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-30.37963727433198</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>17</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>17.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>17.08</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>16.92</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>17.08</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>16.92</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>17.08</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>0</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>0</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-20.98924495364516</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>0</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>17.08</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>16.92</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>17.09</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>16.92</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>17.09</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>0</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>0</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-20.98924495364516</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>0</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>17.14</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>16.92</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>17.11</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>16.92</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>17.11</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>0</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>0</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-20.98924495364516</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>0</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>17.16</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>16.92</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>17.11</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>16.92</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>17.11</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>51.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>30.8</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>30.8</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>0</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-20.98924495364516</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>51</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>51.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>17.18</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>16.92</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>17.13</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>16.92</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>17.13</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>35.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>37.4</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>37.4</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>0</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-18.43034289945595</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>35</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>35.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>16.97</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>16.89</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>17.13</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>16.89</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>17.13</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>17.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>53.6</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>53.6</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>0</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-12.40225628991936</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>17</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>17.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>16.93</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>16.89</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>17.14</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>16.89</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>17.14</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>17.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>56.8</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>56.8</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>0</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-1.419194837369986</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>17</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>17.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>16.81</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>16.87</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>17.15</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>16.87</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>17.15</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>34.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>56.8</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>56.8</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>0</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>14.32157848189232</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>34</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>34.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>16.76</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>16.85</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>17.17</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>16.85</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>17.17</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>84.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>0</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>0</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>34.47548399219946</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>84</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15259,11 +15061,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
           <t>8906</t>
@@ -15445,41 +15243,37 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO35" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AN35" t="inlineStr">
+      <c r="AP35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AP35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AS35" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AT35" t="inlineStr">
         <is>
           <t>0</t>
@@ -15500,20 +15294,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>0</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>0</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15320,10 @@
           <t>0</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>0</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15489,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15673,11 @@
           <t>95.02000000000001</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>95.28</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>96.26</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>95.28</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>96.26000000000001</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15724,16 @@
           <t>5858.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>4471.2</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>4471.2</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>5862.2</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>7957.5</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>7957.5</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15750,10 @@
           <t>-762.703227585248</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>5858</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>5858.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15919,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16103,11 @@
           <t>94.78</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>95.22</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>96.35</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>95.22</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>96.34999999999999</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16154,16 @@
           <t>2316.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>4883.6</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>4883.6</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>6311.9</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>7982.72</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>7982.72</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16180,10 @@
           <t>-898.1634135532122</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>2316</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>2316.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16349,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16533,11 @@
           <t>94.5</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>95.14</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>96.44</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>95.14</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>96.44</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16584,16 @@
           <t>5226.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>6079.8</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>6079.8</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>7106.7</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>8138.98</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>8138.98</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16610,10 @@
           <t>-680.1007001662601</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>5226</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>5226.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16779,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16963,11 @@
           <t>94.5</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>95.08</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>96.54</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>95.08</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>96.54000000000001</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17014,16 @@
           <t>5251.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>6168.0</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>6168</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>7168.0</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>8117.54</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>8117.54</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17040,10 @@
           <t>-656.0789417503911</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>5251</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>5251.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17209,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17393,11 @@
           <t>94.96</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>95.1</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>96.67</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>96.67</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17444,16 @@
           <t>3705.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>5965.0</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>5965</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>7215.0</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>8102.32</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>8102.32</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17470,10 @@
           <t>-601.0093246652077</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>3705</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>3705.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17639,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17823,11 @@
           <t>95.46</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>95.1</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>96.79</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>96.79000000000001</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17874,16 @@
           <t>7920.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>7253.2</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>7253.2</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>7494.4</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>8198.6</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>8198.6</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17900,10 @@
           <t>-335.2309672340452</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>7920</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>7920.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18069,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18253,11 @@
           <t>96.14</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>95.14</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>96.94</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>95.14</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>96.94</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18304,16 @@
           <t>8297.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>7740.2</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>7740.2</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>7531.4</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>8176.92</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>8176.92</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18330,10 @@
           <t>-395.1822077883107</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>8297</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>8297.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18499,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18683,11 @@
           <t>96.5</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>95.18</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>97.07</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>95.18000000000001</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>97.06999999999999</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18734,16 @@
           <t>5667.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>8133.6</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>8133.6</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>8641.2</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>8081.88</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>8081.88</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18760,10 @@
           <t>-507.1060440162501</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>5667</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>5667.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18929,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19113,11 @@
           <t>96.4</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>95.14</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>97.15</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>95.14</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>97.15000000000001</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19164,16 @@
           <t>4236.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>8168.0</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>8168</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>8980.6</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>8209.38</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>8209.379999999999</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19190,10 @@
           <t>-367.1005941984413</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>4236</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>4236.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19359,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19543,11 @@
           <t>96.03999999999999</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>94.97</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>97.22</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>94.97</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>97.22</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19594,16 @@
           <t>10146.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>8465.0</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>8465</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>9210.0</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>8212.94</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>8212.940000000001</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19620,10 @@
           <t>-0.6606446659116045</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>10146</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>10146.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19789,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19973,11 @@
           <t>95.7</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>94.78</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>97.29</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>94.78</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>97.29000000000001</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20024,16 @@
           <t>10355.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>7735.6</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>7735.6</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>9187.7</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>8114.04</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>8114.04</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20050,10 @@
           <t>-110.3656937385167</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>10355</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>10355.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20219,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20403,11 @@
           <t>28.43</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>28.58</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>28.67</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>28.58</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>28.67</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20454,16 @@
           <t>1439.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>1571.8</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>1571.8</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>1616.8</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>1682.58</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>1682.58</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20480,10 @@
           <t>-34.80558693627336</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>1439</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>1439.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20649,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20833,11 @@
           <t>28.4</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>28.58</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>28.67</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>28.58</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>28.67</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20884,16 @@
           <t>1152.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>1518.4</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>1518.4</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>1638.8</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>1695.9</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>1695.9</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20910,10 @@
           <t>-27.91891856328607</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>1152</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>1152.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21079,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21263,11 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>28.6</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>28.68</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>28.68</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21314,16 @@
           <t>1414.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>1601.8</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>1601.8</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>1715.7</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>1693.5</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>1693.5</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21340,10 @@
           <t>13.66628334681286</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>1414</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>1414.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21509,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21693,11 @@
           <t>28.46</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>28.64</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>28.68</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>28.64</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>28.68</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21744,16 @@
           <t>2597.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>1691.6</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>1691.6</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>1954.8</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>1709.22</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>1709.22</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21770,10 @@
           <t>44.51420452742536</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>2597</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>2597.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21939,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22123,11 @@
           <t>28.49</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>28.65</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>28.68</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>28.65</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>28.68</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22174,16 @@
           <t>1257.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>1368.8</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>1368.8</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>1818.8</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>1678.38</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>1678.38</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22200,10 @@
           <t>-39.75712966196534</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>1257</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>1257.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22369,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22553,11 @@
           <t>28.52</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>28.66</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>28.68</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>28.66</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>28.68</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22604,16 @@
           <t>1172.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>1661.8</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>1661.8</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>1794.6</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>1677.4</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>1677.4</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22630,10 @@
           <t>-15.15342387316741</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>1172</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>1172.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22799,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22983,11 @@
           <t>28.53</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>28.68</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>28.67</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>28.68</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>28.67</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23034,16 @@
           <t>1569.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>1759.2</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>1759.2</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>1760.6</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>1675.9</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>1675.9</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23060,10 @@
           <t>29.64306382058567</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>1569</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>1569.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23229,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23413,11 @@
           <t>28.52</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>28.68</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>28.66</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>28.68</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>28.66</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23464,16 @@
           <t>1863.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>1829.6</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>1829.6</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>1712.5</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>1675.9</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>1675.9</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23490,10 @@
           <t>50.04365110378376</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>1863</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>1863.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23659,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23843,11 @@
           <t>28.51</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>28.69</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>28.65</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>28.69</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>28.65</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23894,16 @@
           <t>983.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>2218.0</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>2218</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>1605.5</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>1664.96</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>1664.96</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23920,10 @@
           <t>45.90007396893179</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>983</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>983.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24089,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24273,11 @@
           <t>28.55</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>28.71</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>28.64</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>28.71</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>28.64</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24324,16 @@
           <t>2722.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>2268.8</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>2268.8</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>1615.6</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>1668.06</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>1668.06</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24350,10 @@
           <t>132.6271039916815</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>2722</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>2722.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24519,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24703,11 @@
           <t>28.58</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>28.72</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>28.63</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>28.72</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>28.63</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24754,16 @@
           <t>1659.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>1927.4</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>1927.4</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>1457.3</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>1641.36</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>1641.36</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24780,10 @@
           <t>65.46475031019168</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>1659</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>1659.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24949,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25133,11 @@
           <t>50.96</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>51.47</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>52.21</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>51.47</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>52.21</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25184,16 @@
           <t>17956885.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>8950584.4</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>8950584.4</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>8157639.2</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>6929587.06</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>6929587.06</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25210,10 @@
           <t>693693.9518489158</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>17956885</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>17956885.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25379,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25563,11 @@
           <t>50.48999999999999</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>51.48</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>52.22</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>51.48</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>52.22</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25614,16 @@
           <t>4197152.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>6275232.4</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>6275232.4</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>6626872.5</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>7203813.28</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>7203813.28</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25640,10 @@
           <t>-200974.9605394397</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>4197152</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>4197152.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25809,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25993,11 @@
           <t>50.38</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>51.58</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>52.31</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>51.58</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>52.31</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26044,16 @@
           <t>5019179.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>6863569.0</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>6863569</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>6542082.1</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>7419548.0</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>7419548</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26070,10 @@
           <t>2361.377496462315</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>5019179</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>5019179.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26239,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26423,11 @@
           <t>50.5</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>51.71</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>52.41</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>51.71</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>52.41</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26474,16 @@
           <t>8332853.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>7339532.2</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>7339532.2</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>6379937.7</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>7459733.34</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>7459733.34</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26500,10 @@
           <t>204683.2040657345</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>8332853</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>8332853.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26669,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26853,11 @@
           <t>50.68</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>51.8</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>52.5</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>52.5</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26904,16 @@
           <t>9246853.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>6599368.2</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>6599368.2</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>7443375.8</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>7455734.22</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>7455734.22</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26930,10 @@
           <t>131367.7704480607</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>9246853</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>9246853.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27099,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27283,11 @@
           <t>50.86</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>51.85</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>52.58</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>51.85</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>52.58</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27334,16 @@
           <t>4580125.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>7364694.0</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>7364694</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>7932550.0</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>7814412.12</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>7814412.12</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27360,10 @@
           <t>-75988.84080747515</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>4580125</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>4580125.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27529,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27713,11 @@
           <t>51.27</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>51.96</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>52.72</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>51.96</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>52.72</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27764,16 @@
           <t>7138835.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>6978512.6</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>6978512.6</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>8486901.6</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>7857936.62</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>7857936.62</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27790,10 @@
           <t>130507.8874277407</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>7138835</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>7138835.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27959,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28143,11 @@
           <t>51.64</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>52.07</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>52.85</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>52.07</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>52.85</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28194,16 @@
           <t>7398995.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>6220595.2</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>6220595.2</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>8095639.9</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>7785881.66</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>7785881.66</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28220,10 @@
           <t>146694.7174984878</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>7398995</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>7398995.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28389,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28573,11 @@
           <t>51.84</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>52.13</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>52.96</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>52.13</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>52.96</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28624,16 @@
           <t>4632033.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>5420343.2</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>5420343.2</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>7767470.7</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>7803894.44</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>7803894.44</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28650,10 @@
           <t>136705.377688894</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>4632033</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>4632033.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28819,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29003,11 @@
           <t>51.82000000000001</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>52.17</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>53.05</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>52.17</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>53.05</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29054,16 @@
           <t>13073482.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>8287383.4</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>8287383.4</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>7521303.8</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>7869389.7</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>7869389.7</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29080,10 @@
           <t>414012.7716148719</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>13073482</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>13073482.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29249,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29433,11 @@
           <t>51.73999999999999</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>52.17</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>53.14</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>52.17</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>53.14</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29484,16 @@
           <t>2649218.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>8500406.0</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>8500406</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>6617376.3</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>7740105.52</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>7740105.52</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29510,10 @@
           <t>-109060.9431914054</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>2649218</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>2649218.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29679,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29863,11 @@
           <t>21.32</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>21.72</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>22.36</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>21.72</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>22.36</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29914,16 @@
           <t>2177.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>4399.4</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>4399.4</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>4681.6</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>8321.38</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>8321.379999999999</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29940,10 @@
           <t>-987.1497041315533</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>2177</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>2177.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30109,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30293,11 @@
           <t>21.15</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>21.69</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>22.41</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>21.69</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>22.41</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30344,16 @@
           <t>3433.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>5023.0</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>5023</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>5741.2</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>8405.2</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>8405.200000000001</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30370,10 @@
           <t>-814.8154326973263</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>3433</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>3433.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30539,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30723,11 @@
           <t>21.25</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>21.69</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>22.46</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>21.69</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>22.46</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30774,16 @@
           <t>7998.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>4894.4</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>4894.4</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>8003.0</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>8449.84</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>8449.84</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30800,10 @@
           <t>-674.0944937663835</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>7998</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>7998.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30969,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31153,11 @@
           <t>21.49</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>21.76</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>22.52</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>21.76</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>22.52</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31204,16 @@
           <t>3853.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>4213.2</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>4213.2</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>9406.7</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>8442.96</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>8442.959999999999</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31230,10 @@
           <t>-938.0969205162373</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>3853</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>3853.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31399,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31583,11 @@
           <t>21.91</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>21.78</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>22.59</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>21.78</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>22.59</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31634,16 @@
           <t>4536.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>4421.2</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>4421.2</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>9259.0</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>8584.38</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>8584.379999999999</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31660,10 @@
           <t>-837.6326401404476</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>4536</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>4536.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31829,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32013,11 @@
           <t>22.32</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>21.79</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>22.65</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>21.79</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>22.65</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32064,16 @@
           <t>5295.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>4963.8</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>4963.8</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>8898.1</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>8667.46</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>8667.459999999999</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32090,10 @@
           <t>-737.3753595985891</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>5295</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>5295.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32259,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32443,11 @@
           <t>22.83</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>21.79</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>22.71</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>21.79</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>22.71</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32494,16 @@
           <t>2790.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>6459.4</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>6459.4</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>8480.4</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>8979.34</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>8979.34</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32520,10 @@
           <t>-649.1372674102704</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>2790</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>2790.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32689,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32873,11 @@
           <t>22.97</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>21.76</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>22.75</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>21.76</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>22.75</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32924,16 @@
           <t>4592.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>11111.6</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>11111.6</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>8500.0</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>9360.3</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>9360.299999999999</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32950,10 @@
           <t>-231.5065190194491</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>4592</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>4592.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33119,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33303,11 @@
           <t>23.07</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>21.74</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>22.77</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>21.74</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>22.77</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33354,16 @@
           <t>4893.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>14600.2</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>14600.2</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>8369.4</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>9406.44</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>9406.440000000001</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33380,10 @@
           <t>180.3054972181344</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>4893</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>4893.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33549,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33733,11 @@
           <t>22.61</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>21.69</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>22.73</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>21.69</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>22.73</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33784,16 @@
           <t>7249.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>14096.8</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>14096.8</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>8122.3</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>9347.18</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>9347.18</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33810,10 @@
           <t>729.9188955140344</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>7249</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>7249.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34445,7 +33979,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34629,15 +34163,11 @@
           <t>22.15</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>21.68</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>22.69</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>21.68</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>22.69</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34684,20 +34214,16 @@
           <t>12773.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>12832.4</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>12832.4</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>7573.5</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>9245.3</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>9245.299999999999</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34240,10 @@
           <t>1236.58378966839</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>12773</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>12773.0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
@@ -34881,7 +34409,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>價_量;【b】</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -35065,15 +34593,11 @@
           <t>27.24</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>26.34</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>25.86</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>26.34</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>25.86</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -35120,20 +34644,16 @@
           <t>15398999.0</t>
         </is>
       </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>34221878.6</t>
-        </is>
+      <c r="AX80" t="n">
+        <v>34221878.6</v>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>36617575.1</t>
         </is>
       </c>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>25241855.24</t>
-        </is>
+      <c r="AZ80" t="n">
+        <v>25241855.24</v>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
@@ -35150,8 +34670,10 @@
           <t>2053470.207403455</t>
         </is>
       </c>
-      <c r="BD80" t="n">
-        <v>15398999</v>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>15398999.0</t>
+        </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
@@ -35317,7 +34839,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -35501,15 +35023,11 @@
           <t>27.15</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>26.28</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>25.82</t>
-        </is>
+      <c r="AM81" t="n">
+        <v>26.28</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>25.82</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -35556,20 +35074,16 @@
           <t>31549272.0</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>38918740.8</t>
-        </is>
+      <c r="AX81" t="n">
+        <v>38918740.8</v>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
           <t>36738077.3</t>
         </is>
       </c>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>25462351.56</t>
-        </is>
+      <c r="AZ81" t="n">
+        <v>25462351.56</v>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
@@ -35586,8 +35100,10 @@
           <t>4244409.746218462</t>
         </is>
       </c>
-      <c r="BD81" t="n">
-        <v>31549272</v>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>31549272.0</t>
+        </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
@@ -35753,7 +35269,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -35937,15 +35453,11 @@
           <t>27.09</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>26.21</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>25.79</t>
-        </is>
+      <c r="AM82" t="n">
+        <v>26.21</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>25.79</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -35992,20 +35504,16 @@
           <t>66917706.0</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>44512832.2</t>
-        </is>
+      <c r="AX82" t="n">
+        <v>44512832.2</v>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
           <t>34620079.0</t>
         </is>
       </c>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>25398329.14</t>
-        </is>
+      <c r="AZ82" t="n">
+        <v>25398329.14</v>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
@@ -36022,8 +35530,10 @@
           <t>5492350.917874958</t>
         </is>
       </c>
-      <c r="BD82" t="n">
-        <v>66917706</v>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>66917706.0</t>
+        </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
@@ -36189,7 +35699,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -36373,15 +35883,11 @@
           <t>27.04</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>26.13</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>25.73</t>
-        </is>
+      <c r="AM83" t="n">
+        <v>26.13</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>25.73</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -36428,20 +35934,16 @@
           <t>38460831.0</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>40957668.8</t>
-        </is>
+      <c r="AX83" t="n">
+        <v>40957668.8</v>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
           <t>29797516.3</t>
         </is>
       </c>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>24401116.96</t>
-        </is>
+      <c r="AZ83" t="n">
+        <v>24401116.96</v>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
@@ -36458,8 +35960,10 @@
           <t>3289493.558888707</t>
         </is>
       </c>
-      <c r="BD83" t="n">
-        <v>38460831</v>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>38460831.0</t>
+        </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
@@ -36625,7 +36129,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -36809,15 +36313,11 @@
           <t>26.94</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>26.07</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>25.69</t>
-        </is>
+      <c r="AM84" t="n">
+        <v>26.07</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>25.69</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -36864,20 +36364,16 @@
           <t>18782585.0</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>40170944.4</t>
-        </is>
+      <c r="AX84" t="n">
+        <v>40170944.4</v>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
           <t>26760865.4</t>
         </is>
       </c>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>24094528.78</t>
-        </is>
+      <c r="AZ84" t="n">
+        <v>24094528.78</v>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
@@ -36894,8 +36390,10 @@
           <t>3074023.454662319</t>
         </is>
       </c>
-      <c r="BD84" t="n">
-        <v>18782585</v>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>18782585.0</t>
+        </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -37061,7 +36559,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -37245,15 +36743,11 @@
           <t>26.83</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>26.04</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>25.66</t>
-        </is>
+      <c r="AM85" t="n">
+        <v>26.04</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>25.66</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -37300,20 +36794,16 @@
           <t>38883310.0</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>39013271.6</t>
-        </is>
+      <c r="AX85" t="n">
+        <v>39013271.6</v>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
           <t>27803305.8</t>
         </is>
       </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>23943921.98</t>
-        </is>
+      <c r="AZ85" t="n">
+        <v>23943921.98</v>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
@@ -37330,8 +36820,10 @@
           <t>4764805.968100969</t>
         </is>
       </c>
-      <c r="BD85" t="n">
-        <v>38883310</v>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>38883310.0</t>
+        </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
@@ -37497,7 +36989,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -37681,15 +37173,11 @@
           <t>26.69</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>26.01</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>25.63</t>
-        </is>
+      <c r="AM86" t="n">
+        <v>26.01</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>25.63</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -37736,20 +37224,16 @@
           <t>59519729.0</t>
         </is>
       </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>34557413.8</t>
-        </is>
+      <c r="AX86" t="n">
+        <v>34557413.8</v>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
           <t>25421344.0</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>23374106.74</t>
-        </is>
+      <c r="AZ86" t="n">
+        <v>23374106.74</v>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
@@ -37766,8 +37250,10 @@
           <t>4856388.809866868</t>
         </is>
       </c>
-      <c r="BD86" t="n">
-        <v>59519729</v>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>59519729.0</t>
+        </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
@@ -37933,7 +37419,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -38117,15 +37603,11 @@
           <t>26.45</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>25.95</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>25.59</t>
-        </is>
+      <c r="AM87" t="n">
+        <v>25.95</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>25.59</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -38172,20 +37654,16 @@
           <t>49141889.0</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>24727325.8</t>
-        </is>
+      <c r="AX87" t="n">
+        <v>24727325.8</v>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
           <t>20699524.6</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>22332782.62</t>
-        </is>
+      <c r="AZ87" t="n">
+        <v>22332782.62</v>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
@@ -38202,8 +37680,10 @@
           <t>2602734.090608615</t>
         </is>
       </c>
-      <c r="BD87" t="n">
-        <v>49141889</v>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>49141889.0</t>
+        </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
@@ -38369,7 +37849,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -38553,15 +38033,11 @@
           <t>26.12</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>25.88</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>25.54</t>
-        </is>
+      <c r="AM88" t="n">
+        <v>25.88</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>25.54</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -38608,20 +38084,16 @@
           <t>34527209.0</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>18637363.8</t>
-        </is>
+      <c r="AX88" t="n">
+        <v>18637363.8</v>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>17271105.9</t>
         </is>
       </c>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>21698630.5</t>
-        </is>
+      <c r="AZ88" t="n">
+        <v>21698630.5</v>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
@@ -38638,8 +38110,10 @@
           <t>402183.988432236</t>
         </is>
       </c>
-      <c r="BD88" t="n">
-        <v>34527209</v>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>34527209.0</t>
+        </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
@@ -38805,7 +38279,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -38989,15 +38463,11 @@
           <t>25.93</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>25.84</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
+      <c r="AM89" t="n">
+        <v>25.84</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>25.5</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -39044,20 +38514,16 @@
           <t>12994221.0</t>
         </is>
       </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>13350786.4</t>
-        </is>
+      <c r="AX89" t="n">
+        <v>13350786.4</v>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>15342192.5</t>
         </is>
       </c>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>21347314.02</t>
-        </is>
+      <c r="AZ89" t="n">
+        <v>21347314.02</v>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
@@ -39074,8 +38540,10 @@
           <t>-1189964.157120883</t>
         </is>
       </c>
-      <c r="BD89" t="n">
-        <v>12994221</v>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>12994221.0</t>
+        </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
@@ -39241,7 +38709,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -39425,15 +38893,11 @@
           <t>25.92000000000001</t>
         </is>
       </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>25.82</t>
-        </is>
-      </c>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>25.48</t>
-        </is>
+      <c r="AM90" t="n">
+        <v>25.82</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>25.48</v>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
@@ -39480,20 +38944,16 @@
           <t>16604021.0</t>
         </is>
       </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>16593340.0</t>
-        </is>
+      <c r="AX90" t="n">
+        <v>16593340</v>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
           <t>16535240.3</t>
         </is>
       </c>
-      <c r="AZ90" t="inlineStr">
-        <is>
-          <t>21345209.82</t>
-        </is>
+      <c r="AZ90" t="n">
+        <v>21345209.82</v>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
@@ -39510,8 +38970,10 @@
           <t>-1114856.930871021</t>
         </is>
       </c>
-      <c r="BD90" t="n">
-        <v>16604021</v>
+      <c r="BD90" t="inlineStr">
+        <is>
+          <t>16604021.0</t>
+        </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
